--- a/営業/整骨院web_営業リスト_個別営業文付き.xlsx
+++ b/営業/整骨院web_営業リスト_個別営業文付き.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -531,11 +531,11 @@
     </row>
     <row r="2" ht="200" customHeight="1">
       <c r="A2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>さくら整骨院</t>
+          <t>大名ふわり鍼灸院・整骨院</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -545,17 +545,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>福岡市博多区</t>
+          <t>福岡市中央区</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>東平尾1-1-24-207</t>
+          <t>大名1-9-45-308</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -568,7 +568,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>090-2357-1988</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -578,177 +583,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>【HP未確認】2026年1月開業。東平尾エリア</t>
+          <t>【HP未確認】2026年2月開業。大名エリア</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>さくら整骨院
-ご担当者様
-突然のご連絡失礼いたします。
-整骨院・接骨院専門のホームページ制作・集客支援を行っております、WEBBRIOの柴藤と申します。
-東平尾エリアで2026年1月に開業されたとのこと、おめでとうございます。開業直後でお忙しい日々をお過ごしのことと存じます。
-突然ではございますが、貴院のホームページについてお伺いしたくご連絡いたしました。
-「東平尾 整骨院」「福岡市博多区 整体」などで検索したところ、貴院の公式ホームページが見当たらない状況でした。Googleマップには登録されているかもしれませんが、ホームページがないと、以下のような機会損失が生じている可能性がございます。
-・「どんな先生がいるのか」「どんな施術をしてくれるのか」を知りたい患者様が、情報不足で他院を選んでしまう
-・Googleで「地域名 + 整骨院」と検索しても、貴院の情報が上位に出てこない
-・口コミを書こうとしても、貴院の情報ページが見つからない
-弊社では、整骨院専門で5ページ程度のホームページ制作を98,000円（税込）〜で承っております。スマホ対応、問い合わせフォーム、電話・メール導線、Googleマップ連携、基本SEO設定、公開後1か月サポートが含まれております。
-ホームページだけでなく、Googleビジネスプロフィールの整備、LINE予約導線、Instagram初期設計、チラシ・名刺制作など、施術以外の集客業務を丸ごとサポートしております。
-ご興味がございましたら、貴院の状況に合わせた提案を無料でお作りいたします。お気軽にご連絡ください。
-━━━━━━━━━━━━━━━━━━━━━━
-WEBBRIO
-代表　柴藤
-TEL: 070-7615-5231
-https://seikotsuinweb.com/
-━━━━━━━━━━━━━━━━━━━━━━</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>さくら整骨院様｜Web集客に関するご提案</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="200" customHeight="1">
-      <c r="A3" t="n">
-        <v>12</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>吉村整骨院</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>福岡県</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>福岡市中央区</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>薬院2-14-21-301</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>【HP未確認】2026年3月開業。薬院エリア</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>吉村整骨院
-ご担当者様
-突然のご連絡失礼いたします。
-整骨院・接骨院専門のホームページ制作・集客支援を行っております、WEBBRIOの柴藤と申します。
-薬院エリアで2026年3月に開業されたとのこと、おめでとうございます。開業直後でお忙しい日々をお過ごしのことと存じます。
-突然ではございますが、貴院のホームページについてお伺いしたくご連絡いたしました。
-「薬院 整骨院」「福岡市中央区 整体」などで検索したところ、貴院の公式ホームページが見当たらない状況でした。Googleマップには登録されているかもしれませんが、ホームページがないと、以下のような機会損失が生じている可能性がございます。
-・「どんな先生がいるのか」「どんな施術をしてくれるのか」を知りたい患者様が、情報不足で他院を選んでしまう
-・Googleで「地域名 + 整骨院」と検索しても、貴院の情報が上位に出てこない
-・口コミを書こうとしても、貴院の情報ページが見つからない
-弊社では、整骨院専門で5ページ程度のホームページ制作を98,000円（税込）〜で承っております。スマホ対応、問い合わせフォーム、電話・メール導線、Googleマップ連携、基本SEO設定、公開後1か月サポートが含まれております。
-ホームページだけでなく、Googleビジネスプロフィールの整備、LINE予約導線、Instagram初期設計、チラシ・名刺制作など、施術以外の集客業務を丸ごとサポートしております。
-ご興味がございましたら、貴院の状況に合わせた提案を無料でお作りいたします。お気軽にご連絡ください。
-━━━━━━━━━━━━━━━━━━━━━━
-WEBBRIO
-代表　柴藤
-TEL: 070-7615-5231
-https://seikotsuinweb.com/
-━━━━━━━━━━━━━━━━━━━━━━</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>吉村整骨院様｜Web集客に関するご提案</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="200" customHeight="1">
-      <c r="A4" t="n">
-        <v>13</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>大名ふわり鍼灸院・整骨院</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>福岡県</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>福岡市中央区</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>大名1-9-45-308</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>電話</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>090-2357-1988</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>【HP未確認】2026年2月開業。大名エリア</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>大名ふわり鍼灸院・整骨院
 ご担当者様
@@ -771,70 +609,70 @@
 ━━━━━━━━━━━━━━━━━━━━━━</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>大名ふわり鍼灸院・整骨院様｜Web集客に関するご提案</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="409.6" customHeight="1">
-      <c r="A5" t="n">
+    <row r="3" ht="200" customHeight="1">
+      <c r="A3" t="n">
         <v>14</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>柏原とみた整骨院</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>福岡県</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>福岡市南区</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>柏原6-19-8</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>2026-03-13</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H5" t="n">
+      <c r="H3" t="n">
         <v>1</v>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>電話</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>092-555-8641</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>未確認</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>【HP未確認】2026年3月開業。柏原エリア</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>柏原とみた整骨院
 ご担当者様
@@ -857,70 +695,70 @@
 ━━━━━━━━━━━━━━━━━━━━━━</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>柏原とみた整骨院様｜Web集客に関するご提案</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="409.6" customHeight="1">
-      <c r="A6" t="n">
+    <row r="4" ht="200" customHeight="1">
+      <c r="A4" t="n">
         <v>15</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>しまむら整骨院</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>福岡県</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>福岡市南区</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>大楠3-23-1-101</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H6" t="n">
+      <c r="H4" t="n">
         <v>1</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>電話</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>092-874-3337</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>未確認</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>【HP未確認】2026年1月開業。大楠エリア</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>しまむら整骨院
 ご担当者様
@@ -943,70 +781,70 @@
 ━━━━━━━━━━━━━━━━━━━━━━</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>しまむら整骨院様｜Web集客に関するご提案</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="409.6" customHeight="1">
-      <c r="A7" t="n">
+    <row r="5" ht="409.6" customHeight="1">
+      <c r="A5" t="n">
         <v>16</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>もとむう接骨院</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>福岡県</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>福岡市城南区</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>堤1-13-36 プラモール88 104号</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>2026-01-05</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H7" t="n">
+      <c r="H5" t="n">
         <v>1</v>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>電話</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>092-707-4353</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>未確認</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>【HP未確認】2026年1月開業。堤エリア</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>もとむう接骨院
 ご担当者様
@@ -1029,70 +867,70 @@
 ━━━━━━━━━━━━━━━━━━━━━━</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>もとむう接骨院様｜Web集客に関するご提案</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="409.6" customHeight="1">
-      <c r="A8" t="n">
+    <row r="6" ht="409.6" customHeight="1">
+      <c r="A6" t="n">
         <v>17</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>三好整骨院</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>福岡県</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>福岡市城南区</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>七隈1-17-29</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H8" t="n">
+      <c r="H6" t="n">
         <v>1</v>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>電話</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>092-843-0033</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>未確認</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>【HP未確認】2026年1月開業。七隈エリア</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>三好整骨院
 ご担当者様
@@ -1115,70 +953,70 @@
 ━━━━━━━━━━━━━━━━━━━━━━</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>三好整骨院様｜Web集客に関するご提案</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="409.6" customHeight="1">
-      <c r="A9" t="n">
+    <row r="7" ht="409.6" customHeight="1">
+      <c r="A7" t="n">
         <v>18</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>ますみ整骨院</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>福岡県</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>福岡市早良区</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>田村7-14-88</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H9" t="n">
+      <c r="H7" t="n">
         <v>1</v>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>電話</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>092-982-4972</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>未確認</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>【HP未確認】2026年4月開業。田村エリア</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>ますみ整骨院
 ご担当者様
@@ -1201,65 +1039,65 @@
 ━━━━━━━━━━━━━━━━━━━━━━</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>ますみ整骨院様｜Web集客に関するご提案</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="409.6" customHeight="1">
-      <c r="A10" t="n">
+    <row r="8" ht="409.6" customHeight="1">
+      <c r="A8" t="n">
         <v>19</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>賀茂整骨院</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>福岡県</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>福岡市早良区</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>田隈1-25-20</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>2026-03-03</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H10" t="n">
+      <c r="H8" t="n">
         <v>1</v>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>未確認</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>【HP未確認】2026年3月開業。田隈エリア</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>賀茂整骨院
 ご担当者様
@@ -1282,65 +1120,65 @@
 ━━━━━━━━━━━━━━━━━━━━━━</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>賀茂整骨院様｜Web集客に関するご提案</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="409.6" customHeight="1">
-      <c r="A11" t="n">
+    <row r="9" ht="409.6" customHeight="1">
+      <c r="A9" t="n">
         <v>20</v>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>野方たかまる整骨院</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>福岡県</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>福岡市西区</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>野方1-17-29 野方宮本ビル1階2号</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>2026-04-24</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H11" t="n">
+      <c r="H9" t="n">
         <v>1</v>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>未確認</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>【HP未確認】2026年4月開業。野方エリア</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>野方たかまる整骨院
 ご担当者様
@@ -1363,65 +1201,65 @@
 ━━━━━━━━━━━━━━━━━━━━━━</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>野方たかまる整骨院様｜Web集客に関するご提案</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="409.6" customHeight="1">
-      <c r="A12" t="n">
+    <row r="10" ht="409.6" customHeight="1">
+      <c r="A10" t="n">
         <v>21</v>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>まつおか整骨院・鍼灸院</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>福岡県</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>福岡市西区</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>今宿1-5-30 第1井原ビル102</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H12" t="n">
+      <c r="H10" t="n">
         <v>1</v>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>未確認</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>【HP未確認】2026年4月開業。今宿エリア</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>まつおか整骨院・鍼灸院
 ご担当者様
@@ -1444,70 +1282,70 @@
 ━━━━━━━━━━━━━━━━━━━━━━</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>まつおか整骨院・鍼灸院様｜Web集客に関するご提案</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="409.6" customHeight="1">
-      <c r="A13" t="n">
+    <row r="11" ht="409.6" customHeight="1">
+      <c r="A11" t="n">
         <v>22</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>いまいけ接骨院</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>愛知県</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>名古屋市千種区</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>今池3-2-9 ママビル1F</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H13" t="n">
+      <c r="H11" t="n">
         <v>1</v>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>電話・Facebook</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>052-732-8727</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>未確認</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>【HP未確認】2026年3月開業。今池エリア。Facebookあり</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>いまいけ接骨院
 ご担当者様
@@ -1530,65 +1368,65 @@
 ━━━━━━━━━━━━━━━━━━━━━━</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>いまいけ接骨院様｜Web集客に関するご提案</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="409.6" customHeight="1">
-      <c r="A14" t="n">
+    <row r="12" ht="409.6" customHeight="1">
+      <c r="A12" t="n">
         <v>23</v>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>ちくさ接骨院</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>愛知県</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>名古屋市千種区</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>千種1-16-16</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H14" t="n">
+      <c r="H12" t="n">
         <v>1</v>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>未確認</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>【HP未確認】2026年3月開業。千種エリア</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>ちくさ接骨院
 ご担当者様
@@ -1611,70 +1449,70 @@
 ━━━━━━━━━━━━━━━━━━━━━━</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>ちくさ接骨院様｜Web集客に関するご提案</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="409.6" customHeight="1">
-      <c r="A15" t="n">
+    <row r="13" ht="409.6" customHeight="1">
+      <c r="A13" t="n">
         <v>24</v>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>しんもりやま整骨院</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>愛知県</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>名古屋市守山区</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>新守町6-1</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>2026-01-15</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H15" t="n">
+      <c r="H13" t="n">
         <v>1</v>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>電話</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>052-778-8880</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>未確認</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>【HP未確認】2026年1月開業。新守山駅徒歩1分</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>しんもりやま整骨院
 ご担当者様
@@ -1697,70 +1535,70 @@
 ━━━━━━━━━━━━━━━━━━━━━━</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>しんもりやま整骨院様｜Web集客に関するご提案</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="409.6" customHeight="1">
-      <c r="A16" t="n">
+    <row r="14" ht="409.6" customHeight="1">
+      <c r="A14" t="n">
         <v>25</v>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>鍼灸整骨院三六 福岡南院</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>福岡県</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>福岡市南区</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>老司2-4-27</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H16" t="n">
+      <c r="H14" t="n">
         <v>3</v>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>LINE・電話</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>https://tir-sanroku.jp/shop/fukuoka/</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>https://tir-sanroku.jp/shop/fukuoka/</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>三六グループ福岡新院。LINE予約可</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>鍼灸整骨院三六 福岡南院
 ご担当者様
@@ -1781,70 +1619,70 @@
 ━━━━━━━━━━━━━━━━━━━━━━</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>鍼灸整骨院三六 福岡南院様｜Web集客に関するご提案</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="409.6" customHeight="1">
-      <c r="A17" t="n">
+    <row r="15" ht="409.6" customHeight="1">
+      <c r="A15" t="n">
         <v>26</v>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>なぎさ接骨院・鍼灸院</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>広島県</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>広島市東区</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>牛田本町2-8-5</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H17" t="n">
+      <c r="H15" t="n">
         <v>3</v>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>LINE・電話</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>https://nagisasekkotsuin.jp/</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>https://nagisasekkotsuin.jp/</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>2026年4月開業。公式HP有、LINE予約対応</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>なぎさ接骨院・鍼灸院
 ご担当者様
@@ -1864,70 +1702,70 @@
 ━━━━━━━━━━━━━━━━━━━━━━</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>なぎさ接骨院・鍼灸院様｜Web集客に関するご提案</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="409.6" customHeight="1">
-      <c r="A18" t="n">
+    <row r="16" ht="409.6" customHeight="1">
+      <c r="A16" t="n">
         <v>27</v>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>ひろがる接骨院 広島スタジアム前院</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>広島県</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>広島市南区</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>南蟹屋1-1-25</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>2026-02-20</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H18" t="n">
+      <c r="H16" t="n">
         <v>5</v>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>LINE・電話・HotPepper</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>https://hirogaru-hiroshima.com/</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>https://hirogaru-hiroshima.com/</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>充実した公式HP。新規制作対象外だがコンサル提案可</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>ひろがる接骨院 広島スタジアム前院
 ご担当者様
@@ -1950,70 +1788,70 @@
 ━━━━━━━━━━━━━━━━━━━━━━</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>ひろがる接骨院 広島スタジアム前院様｜Web集客に関するご提案</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="409.6" customHeight="1">
-      <c r="A19" t="n">
+    <row r="17" ht="409.6" customHeight="1">
+      <c r="A17" t="n">
         <v>28</v>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>with.鍼灸整骨院 西明石院</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>兵庫県</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>明石市</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>和坂13-6 プラスパ西明石102</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H19" t="n">
+      <c r="H17" t="n">
         <v>3</v>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>LINE・電話</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>https://with-seikotsuin.com/</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>https://with-seikotsuin.com/</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>2026年6月開業。グループ公式HP有</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>with.鍼灸整骨院 西明石院
 ご担当者様
@@ -2033,12 +1871,14 @@
 ━━━━━━━━━━━━━━━━━━━━━━</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>with.鍼灸整骨院 西明石院様｜Web集客に関するご提案</t>
         </is>
       </c>
     </row>
+    <row r="18" ht="409.6" customHeight="1"/>
+    <row r="19" ht="409.6" customHeight="1"/>
     <row r="20" ht="409.6" customHeight="1"/>
     <row r="21" ht="409.6" customHeight="1"/>
     <row r="22" ht="409.6" customHeight="1"/>
@@ -2062,7 +1902,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N43"/>
+  <dimension ref="A1:N45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5577,6 +5417,168 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>11</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>さくら整骨院</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>福岡県</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>福岡市博多区</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>東平尾1-1-24-207</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>手動送信（フォームなし）</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>【HP未確認】2026年1月開業。東平尾エリア</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>さくら整骨院
+ご担当者様
+突然のご連絡失礼いたします。
+整骨院・接骨院専門のホームページ制作・集客支援を行っております、WEBBRIOの柴藤と申します。
+東平尾エリアで2026年1月に開業されたとのこと、おめでとうございます。開業直後でお忙しい日々をお過ごしのことと存じます。
+突然ではございますが、貴院のホームページについてお伺いしたくご連絡いたしました。
+「東平尾 整骨院」「福岡市博多区 整体」などで検索したところ、貴院の公式ホームページが見当たらない状況でした。Googleマップには登録されているかもしれませんが、ホームページがないと、以下のような機会損失が生じている可能性がございます。
+・「どんな先生がいるのか」「どんな施術をしてくれるのか」を知りたい患者様が、情報不足で他院を選んでしまう
+・Googleで「地域名 + 整骨院」と検索しても、貴院の情報が上位に出てこない
+・口コミを書こうとしても、貴院の情報ページが見つからない
+弊社では、整骨院専門で5ページ程度のホームページ制作を98,000円（税込）〜で承っております。スマホ対応、問い合わせフォーム、電話・メール導線、Googleマップ連携、基本SEO設定、公開後1か月サポートが含まれております。
+ホームページだけでなく、Googleビジネスプロフィールの整備、LINE予約導線、Instagram初期設計、チラシ・名刺制作など、施術以外の集客業務を丸ごとサポートしております。
+ご興味がございましたら、貴院の状況に合わせた提案を無料でお作りいたします。お気軽にご連絡ください。
+━━━━━━━━━━━━━━━━━━━━━━
+WEBBRIO
+代表　柴藤
+TEL: 070-7615-5231
+https://seikotsuinweb.com/
+━━━━━━━━━━━━━━━━━━━━━━</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>さくら整骨院様｜Web集客に関するご提案</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>12</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>吉村整骨院</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>福岡県</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>福岡市中央区</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>薬院2-14-21-301</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>手動送信（フォームなし）</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>【HP未確認】2026年3月開業。薬院エリア</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>吉村整骨院
+ご担当者様
+突然のご連絡失礼いたします。
+整骨院・接骨院専門のホームページ制作・集客支援を行っております、WEBBRIOの柴藤と申します。
+薬院エリアで2026年3月に開業されたとのこと、おめでとうございます。開業直後でお忙しい日々をお過ごしのことと存じます。
+突然ではございますが、貴院のホームページについてお伺いしたくご連絡いたしました。
+「薬院 整骨院」「福岡市中央区 整体」などで検索したところ、貴院の公式ホームページが見当たらない状況でした。Googleマップには登録されているかもしれませんが、ホームページがないと、以下のような機会損失が生じている可能性がございます。
+・「どんな先生がいるのか」「どんな施術をしてくれるのか」を知りたい患者様が、情報不足で他院を選んでしまう
+・Googleで「地域名 + 整骨院」と検索しても、貴院の情報が上位に出てこない
+・口コミを書こうとしても、貴院の情報ページが見つからない
+弊社では、整骨院専門で5ページ程度のホームページ制作を98,000円（税込）〜で承っております。スマホ対応、問い合わせフォーム、電話・メール導線、Googleマップ連携、基本SEO設定、公開後1か月サポートが含まれております。
+ホームページだけでなく、Googleビジネスプロフィールの整備、LINE予約導線、Instagram初期設計、チラシ・名刺制作など、施術以外の集客業務を丸ごとサポートしております。
+ご興味がございましたら、貴院の状況に合わせた提案を無料でお作りいたします。お気軽にご連絡ください。
+━━━━━━━━━━━━━━━━━━━━━━
+WEBBRIO
+代表　柴藤
+TEL: 070-7615-5231
+https://seikotsuinweb.com/
+━━━━━━━━━━━━━━━━━━━━━━</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>吉村整骨院様｜Web集客に関するご提案</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/営業/整骨院web_営業リスト_個別営業文付き.xlsx
+++ b/営業/整骨院web_営業リスト_個別営業文付き.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -529,1354 +529,22 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="200" customHeight="1">
-      <c r="A2" t="n">
-        <v>13</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>大名ふわり鍼灸院・整骨院</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>福岡県</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>福岡市中央区</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>大名1-9-45-308</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>電話</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>090-2357-1988</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>【HP未確認】2026年2月開業。大名エリア</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>大名ふわり鍼灸院・整骨院
-ご担当者様
-突然のご連絡失礼いたします。
-整骨院・接骨院専門のホームページ制作・集客支援を行っております、WEBBRIOの柴藤と申します。
-大名エリアで2026年2月に開業されたとのこと、おめでとうございます。開業直後でお忙しい日々をお過ごしのことと存じます。
-突然ではございますが、貴院のホームページについてお伺いしたくご連絡いたしました。
-「大名 整骨院」「福岡市中央区 整体」などで検索したところ、貴院の公式ホームページが見当たらない状況でした。Googleマップには登録されているかもしれませんが、ホームページがないと、以下のような機会損失が生じている可能性がございます。
-・「どんな先生がいるのか」「どんな施術をしてくれるのか」を知りたい患者様が、情報不足で他院を選んでしまう
-・Googleで「地域名 + 整骨院」と検索しても、貴院の情報が上位に出てこない
-・口コミを書こうとしても、貴院の情報ページが見つからない
-弊社では、整骨院専門で5ページ程度のホームページ制作を98,000円（税込）〜で承っております。スマホ対応、問い合わせフォーム、電話・メール導線、Googleマップ連携、基本SEO設定、公開後1か月サポートが含まれております。
-ホームページだけでなく、Googleビジネスプロフィールの整備、LINE予約導線、Instagram初期設計、チラシ・名刺制作など、施術以外の集客業務を丸ごとサポートしております。
-ご興味がございましたら、貴院の状況に合わせた提案を無料でお作りいたします。お気軽にご連絡ください。
-━━━━━━━━━━━━━━━━━━━━━━
-WEBBRIO
-代表　柴藤
-TEL: 070-7615-5231
-https://seikotsuinweb.com/
-━━━━━━━━━━━━━━━━━━━━━━</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>大名ふわり鍼灸院・整骨院様｜Web集客に関するご提案</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="200" customHeight="1">
-      <c r="A3" t="n">
-        <v>14</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>柏原とみた整骨院</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>福岡県</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>福岡市南区</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>柏原6-19-8</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>電話</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>092-555-8641</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>【HP未確認】2026年3月開業。柏原エリア</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>柏原とみた整骨院
-ご担当者様
-突然のご連絡失礼いたします。
-整骨院・接骨院専門のホームページ制作・集客支援を行っております、WEBBRIOの柴藤と申します。
-柏原エリアで2026年3月に開業されたとのこと、おめでとうございます。開業直後でお忙しい日々をお過ごしのことと存じます。
-突然ではございますが、貴院のホームページについてお伺いしたくご連絡いたしました。
-「柏原 整骨院」「福岡市南区 整体」などで検索したところ、貴院の公式ホームページが見当たらない状況でした。Googleマップには登録されているかもしれませんが、ホームページがないと、以下のような機会損失が生じている可能性がございます。
-・「どんな先生がいるのか」「どんな施術をしてくれるのか」を知りたい患者様が、情報不足で他院を選んでしまう
-・Googleで「地域名 + 整骨院」と検索しても、貴院の情報が上位に出てこない
-・口コミを書こうとしても、貴院の情報ページが見つからない
-弊社では、整骨院専門で5ページ程度のホームページ制作を98,000円（税込）〜で承っております。スマホ対応、問い合わせフォーム、電話・メール導線、Googleマップ連携、基本SEO設定、公開後1か月サポートが含まれております。
-ホームページだけでなく、Googleビジネスプロフィールの整備、LINE予約導線、Instagram初期設計、チラシ・名刺制作など、施術以外の集客業務を丸ごとサポートしております。
-ご興味がございましたら、貴院の状況に合わせた提案を無料でお作りいたします。お気軽にご連絡ください。
-━━━━━━━━━━━━━━━━━━━━━━
-WEBBRIO
-代表　柴藤
-TEL: 070-7615-5231
-https://seikotsuinweb.com/
-━━━━━━━━━━━━━━━━━━━━━━</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>柏原とみた整骨院様｜Web集客に関するご提案</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="200" customHeight="1">
-      <c r="A4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>しまむら整骨院</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>福岡県</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>福岡市南区</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>大楠3-23-1-101</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>電話</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>092-874-3337</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>【HP未確認】2026年1月開業。大楠エリア</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>しまむら整骨院
-ご担当者様
-突然のご連絡失礼いたします。
-整骨院・接骨院専門のホームページ制作・集客支援を行っております、WEBBRIOの柴藤と申します。
-大楠エリアで2026年1月に開業されたとのこと、おめでとうございます。開業直後でお忙しい日々をお過ごしのことと存じます。
-突然ではございますが、貴院のホームページについてお伺いしたくご連絡いたしました。
-「大楠 整骨院」「福岡市南区 整体」などで検索したところ、貴院の公式ホームページが見当たらない状況でした。Googleマップには登録されているかもしれませんが、ホームページがないと、以下のような機会損失が生じている可能性がございます。
-・「どんな先生がいるのか」「どんな施術をしてくれるのか」を知りたい患者様が、情報不足で他院を選んでしまう
-・Googleで「地域名 + 整骨院」と検索しても、貴院の情報が上位に出てこない
-・口コミを書こうとしても、貴院の情報ページが見つからない
-弊社では、整骨院専門で5ページ程度のホームページ制作を98,000円（税込）〜で承っております。スマホ対応、問い合わせフォーム、電話・メール導線、Googleマップ連携、基本SEO設定、公開後1か月サポートが含まれております。
-ホームページだけでなく、Googleビジネスプロフィールの整備、LINE予約導線、Instagram初期設計、チラシ・名刺制作など、施術以外の集客業務を丸ごとサポートしております。
-ご興味がございましたら、貴院の状況に合わせた提案を無料でお作りいたします。お気軽にご連絡ください。
-━━━━━━━━━━━━━━━━━━━━━━
-WEBBRIO
-代表　柴藤
-TEL: 070-7615-5231
-https://seikotsuinweb.com/
-━━━━━━━━━━━━━━━━━━━━━━</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>しまむら整骨院様｜Web集客に関するご提案</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="409.6" customHeight="1">
-      <c r="A5" t="n">
-        <v>16</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>もとむう接骨院</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>福岡県</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>福岡市城南区</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>堤1-13-36 プラモール88 104号</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-01-05</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>電話</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>092-707-4353</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>【HP未確認】2026年1月開業。堤エリア</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>もとむう接骨院
-ご担当者様
-突然のご連絡失礼いたします。
-整骨院・接骨院専門のホームページ制作・集客支援を行っております、WEBBRIOの柴藤と申します。
-堤エリアで2026年1月に開業されたとのこと、おめでとうございます。開業直後でお忙しい日々をお過ごしのことと存じます。
-突然ではございますが、貴院のホームページについてお伺いしたくご連絡いたしました。
-「堤 整骨院」「福岡市城南区 整体」などで検索したところ、貴院の公式ホームページが見当たらない状況でした。Googleマップには登録されているかもしれませんが、ホームページがないと、以下のような機会損失が生じている可能性がございます。
-・「どんな先生がいるのか」「どんな施術をしてくれるのか」を知りたい患者様が、情報不足で他院を選んでしまう
-・Googleで「地域名 + 整骨院」と検索しても、貴院の情報が上位に出てこない
-・口コミを書こうとしても、貴院の情報ページが見つからない
-弊社では、整骨院専門で5ページ程度のホームページ制作を98,000円（税込）〜で承っております。スマホ対応、問い合わせフォーム、電話・メール導線、Googleマップ連携、基本SEO設定、公開後1か月サポートが含まれております。
-ホームページだけでなく、Googleビジネスプロフィールの整備、LINE予約導線、Instagram初期設計、チラシ・名刺制作など、施術以外の集客業務を丸ごとサポートしております。
-ご興味がございましたら、貴院の状況に合わせた提案を無料でお作りいたします。お気軽にご連絡ください。
-━━━━━━━━━━━━━━━━━━━━━━
-WEBBRIO
-代表　柴藤
-TEL: 070-7615-5231
-https://seikotsuinweb.com/
-━━━━━━━━━━━━━━━━━━━━━━</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>もとむう接骨院様｜Web集客に関するご提案</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="409.6" customHeight="1">
-      <c r="A6" t="n">
-        <v>17</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>三好整骨院</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>福岡県</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>福岡市城南区</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>七隈1-17-29</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>電話</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>092-843-0033</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>【HP未確認】2026年1月開業。七隈エリア</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>三好整骨院
-ご担当者様
-突然のご連絡失礼いたします。
-整骨院・接骨院専門のホームページ制作・集客支援を行っております、WEBBRIOの柴藤と申します。
-七隈エリアで2026年1月に開業されたとのこと、おめでとうございます。開業直後でお忙しい日々をお過ごしのことと存じます。
-突然ではございますが、貴院のホームページについてお伺いしたくご連絡いたしました。
-「七隈 整骨院」「福岡市城南区 整体」などで検索したところ、貴院の公式ホームページが見当たらない状況でした。Googleマップには登録されているかもしれませんが、ホームページがないと、以下のような機会損失が生じている可能性がございます。
-・「どんな先生がいるのか」「どんな施術をしてくれるのか」を知りたい患者様が、情報不足で他院を選んでしまう
-・Googleで「地域名 + 整骨院」と検索しても、貴院の情報が上位に出てこない
-・口コミを書こうとしても、貴院の情報ページが見つからない
-弊社では、整骨院専門で5ページ程度のホームページ制作を98,000円（税込）〜で承っております。スマホ対応、問い合わせフォーム、電話・メール導線、Googleマップ連携、基本SEO設定、公開後1か月サポートが含まれております。
-ホームページだけでなく、Googleビジネスプロフィールの整備、LINE予約導線、Instagram初期設計、チラシ・名刺制作など、施術以外の集客業務を丸ごとサポートしております。
-ご興味がございましたら、貴院の状況に合わせた提案を無料でお作りいたします。お気軽にご連絡ください。
-━━━━━━━━━━━━━━━━━━━━━━
-WEBBRIO
-代表　柴藤
-TEL: 070-7615-5231
-https://seikotsuinweb.com/
-━━━━━━━━━━━━━━━━━━━━━━</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>三好整骨院様｜Web集客に関するご提案</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="409.6" customHeight="1">
-      <c r="A7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>ますみ整骨院</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>福岡県</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>福岡市早良区</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>田村7-14-88</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>電話</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>092-982-4972</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>【HP未確認】2026年4月開業。田村エリア</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>ますみ整骨院
-ご担当者様
-突然のご連絡失礼いたします。
-整骨院・接骨院専門のホームページ制作・集客支援を行っております、WEBBRIOの柴藤と申します。
-田村エリアで2026年4月に開業されたとのこと、おめでとうございます。開業直後でお忙しい日々をお過ごしのことと存じます。
-突然ではございますが、貴院のホームページについてお伺いしたくご連絡いたしました。
-「田村 整骨院」「福岡市早良区 整体」などで検索したところ、貴院の公式ホームページが見当たらない状況でした。Googleマップには登録されているかもしれませんが、ホームページがないと、以下のような機会損失が生じている可能性がございます。
-・「どんな先生がいるのか」「どんな施術をしてくれるのか」を知りたい患者様が、情報不足で他院を選んでしまう
-・Googleで「地域名 + 整骨院」と検索しても、貴院の情報が上位に出てこない
-・口コミを書こうとしても、貴院の情報ページが見つからない
-弊社では、整骨院専門で5ページ程度のホームページ制作を98,000円（税込）〜で承っております。スマホ対応、問い合わせフォーム、電話・メール導線、Googleマップ連携、基本SEO設定、公開後1か月サポートが含まれております。
-ホームページだけでなく、Googleビジネスプロフィールの整備、LINE予約導線、Instagram初期設計、チラシ・名刺制作など、施術以外の集客業務を丸ごとサポートしております。
-ご興味がございましたら、貴院の状況に合わせた提案を無料でお作りいたします。お気軽にご連絡ください。
-━━━━━━━━━━━━━━━━━━━━━━
-WEBBRIO
-代表　柴藤
-TEL: 070-7615-5231
-https://seikotsuinweb.com/
-━━━━━━━━━━━━━━━━━━━━━━</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>ますみ整骨院様｜Web集客に関するご提案</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="409.6" customHeight="1">
-      <c r="A8" t="n">
-        <v>19</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>賀茂整骨院</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>福岡県</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>福岡市早良区</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>田隈1-25-20</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>【HP未確認】2026年3月開業。田隈エリア</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>賀茂整骨院
-ご担当者様
-突然のご連絡失礼いたします。
-整骨院・接骨院専門のホームページ制作・集客支援を行っております、WEBBRIOの柴藤と申します。
-田隈エリアで2026年3月に開業されたとのこと、おめでとうございます。開業直後でお忙しい日々をお過ごしのことと存じます。
-突然ではございますが、貴院のホームページについてお伺いしたくご連絡いたしました。
-「田隈 整骨院」「福岡市早良区 整体」などで検索したところ、貴院の公式ホームページが見当たらない状況でした。Googleマップには登録されているかもしれませんが、ホームページがないと、以下のような機会損失が生じている可能性がございます。
-・「どんな先生がいるのか」「どんな施術をしてくれるのか」を知りたい患者様が、情報不足で他院を選んでしまう
-・Googleで「地域名 + 整骨院」と検索しても、貴院の情報が上位に出てこない
-・口コミを書こうとしても、貴院の情報ページが見つからない
-弊社では、整骨院専門で5ページ程度のホームページ制作を98,000円（税込）〜で承っております。スマホ対応、問い合わせフォーム、電話・メール導線、Googleマップ連携、基本SEO設定、公開後1か月サポートが含まれております。
-ホームページだけでなく、Googleビジネスプロフィールの整備、LINE予約導線、Instagram初期設計、チラシ・名刺制作など、施術以外の集客業務を丸ごとサポートしております。
-ご興味がございましたら、貴院の状況に合わせた提案を無料でお作りいたします。お気軽にご連絡ください。
-━━━━━━━━━━━━━━━━━━━━━━
-WEBBRIO
-代表　柴藤
-TEL: 070-7615-5231
-https://seikotsuinweb.com/
-━━━━━━━━━━━━━━━━━━━━━━</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>賀茂整骨院様｜Web集客に関するご提案</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="409.6" customHeight="1">
-      <c r="A9" t="n">
-        <v>20</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>野方たかまる整骨院</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>福岡県</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>福岡市西区</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>野方1-17-29 野方宮本ビル1階2号</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>【HP未確認】2026年4月開業。野方エリア</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>野方たかまる整骨院
-ご担当者様
-突然のご連絡失礼いたします。
-整骨院・接骨院専門のホームページ制作・集客支援を行っております、WEBBRIOの柴藤と申します。
-野方エリアで2026年4月に開業されたとのこと、おめでとうございます。開業直後でお忙しい日々をお過ごしのことと存じます。
-突然ではございますが、貴院のホームページについてお伺いしたくご連絡いたしました。
-「野方 整骨院」「福岡市西区 整体」などで検索したところ、貴院の公式ホームページが見当たらない状況でした。Googleマップには登録されているかもしれませんが、ホームページがないと、以下のような機会損失が生じている可能性がございます。
-・「どんな先生がいるのか」「どんな施術をしてくれるのか」を知りたい患者様が、情報不足で他院を選んでしまう
-・Googleで「地域名 + 整骨院」と検索しても、貴院の情報が上位に出てこない
-・口コミを書こうとしても、貴院の情報ページが見つからない
-弊社では、整骨院専門で5ページ程度のホームページ制作を98,000円（税込）〜で承っております。スマホ対応、問い合わせフォーム、電話・メール導線、Googleマップ連携、基本SEO設定、公開後1か月サポートが含まれております。
-ホームページだけでなく、Googleビジネスプロフィールの整備、LINE予約導線、Instagram初期設計、チラシ・名刺制作など、施術以外の集客業務を丸ごとサポートしております。
-ご興味がございましたら、貴院の状況に合わせた提案を無料でお作りいたします。お気軽にご連絡ください。
-━━━━━━━━━━━━━━━━━━━━━━
-WEBBRIO
-代表　柴藤
-TEL: 070-7615-5231
-https://seikotsuinweb.com/
-━━━━━━━━━━━━━━━━━━━━━━</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>野方たかまる整骨院様｜Web集客に関するご提案</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="409.6" customHeight="1">
-      <c r="A10" t="n">
-        <v>21</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>まつおか整骨院・鍼灸院</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>福岡県</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>福岡市西区</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>今宿1-5-30 第1井原ビル102</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>【HP未確認】2026年4月開業。今宿エリア</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>まつおか整骨院・鍼灸院
-ご担当者様
-突然のご連絡失礼いたします。
-整骨院・接骨院専門のホームページ制作・集客支援を行っております、WEBBRIOの柴藤と申します。
-今宿エリアで2026年4月に開業されたとのこと、おめでとうございます。開業直後でお忙しい日々をお過ごしのことと存じます。
-突然ではございますが、貴院のホームページについてお伺いしたくご連絡いたしました。
-「今宿 整骨院」「福岡市西区 整体」などで検索したところ、貴院の公式ホームページが見当たらない状況でした。Googleマップには登録されているかもしれませんが、ホームページがないと、以下のような機会損失が生じている可能性がございます。
-・「どんな先生がいるのか」「どんな施術をしてくれるのか」を知りたい患者様が、情報不足で他院を選んでしまう
-・Googleで「地域名 + 整骨院」と検索しても、貴院の情報が上位に出てこない
-・口コミを書こうとしても、貴院の情報ページが見つからない
-弊社では、整骨院専門で5ページ程度のホームページ制作を98,000円（税込）〜で承っております。スマホ対応、問い合わせフォーム、電話・メール導線、Googleマップ連携、基本SEO設定、公開後1か月サポートが含まれております。
-ホームページだけでなく、Googleビジネスプロフィールの整備、LINE予約導線、Instagram初期設計、チラシ・名刺制作など、施術以外の集客業務を丸ごとサポートしております。
-ご興味がございましたら、貴院の状況に合わせた提案を無料でお作りいたします。お気軽にご連絡ください。
-━━━━━━━━━━━━━━━━━━━━━━
-WEBBRIO
-代表　柴藤
-TEL: 070-7615-5231
-https://seikotsuinweb.com/
-━━━━━━━━━━━━━━━━━━━━━━</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>まつおか整骨院・鍼灸院様｜Web集客に関するご提案</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="409.6" customHeight="1">
-      <c r="A11" t="n">
-        <v>22</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>いまいけ接骨院</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>愛知県</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>名古屋市千種区</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>今池3-2-9 ママビル1F</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>電話・Facebook</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>052-732-8727</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>【HP未確認】2026年3月開業。今池エリア。Facebookあり</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>いまいけ接骨院
-ご担当者様
-突然のご連絡失礼いたします。
-整骨院・接骨院専門のホームページ制作・集客支援を行っております、WEBBRIOの柴藤と申します。
-今池エリアで2026年3月に開業されたとのこと、おめでとうございます。開業直後でお忙しい日々をお過ごしのことと存じます。
-突然ではございますが、貴院のホームページについてお伺いしたくご連絡いたしました。
-「今池 整骨院」「名古屋市千種区 整体」などで検索したところ、貴院の公式ホームページが見当たらない状況でした。Googleマップには登録されているかもしれませんが、ホームページがないと、以下のような機会損失が生じている可能性がございます。
-・「どんな先生がいるのか」「どんな施術をしてくれるのか」を知りたい患者様が、情報不足で他院を選んでしまう
-・Googleで「地域名 + 整骨院」と検索しても、貴院の情報が上位に出てこない
-・口コミを書こうとしても、貴院の情報ページが見つからない
-弊社では、整骨院専門で5ページ程度のホームページ制作を98,000円（税込）〜で承っております。スマホ対応、問い合わせフォーム、電話・メール導線、Googleマップ連携、基本SEO設定、公開後1か月サポートが含まれております。
-ホームページだけでなく、Googleビジネスプロフィールの整備、LINE予約導線、Instagram初期設計、チラシ・名刺制作など、施術以外の集客業務を丸ごとサポートしております。
-ご興味がございましたら、貴院の状況に合わせた提案を無料でお作りいたします。お気軽にご連絡ください。
-━━━━━━━━━━━━━━━━━━━━━━
-WEBBRIO
-代表　柴藤
-TEL: 070-7615-5231
-https://seikotsuinweb.com/
-━━━━━━━━━━━━━━━━━━━━━━</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>いまいけ接骨院様｜Web集客に関するご提案</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="409.6" customHeight="1">
-      <c r="A12" t="n">
-        <v>23</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>ちくさ接骨院</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>愛知県</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>名古屋市千種区</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>千種1-16-16</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>【HP未確認】2026年3月開業。千種エリア</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>ちくさ接骨院
-ご担当者様
-突然のご連絡失礼いたします。
-整骨院・接骨院専門のホームページ制作・集客支援を行っております、WEBBRIOの柴藤と申します。
-千種エリアで2026年3月に開業されたとのこと、おめでとうございます。開業直後でお忙しい日々をお過ごしのことと存じます。
-突然ではございますが、貴院のホームページについてお伺いしたくご連絡いたしました。
-「千種 整骨院」「名古屋市千種区 整体」などで検索したところ、貴院の公式ホームページが見当たらない状況でした。Googleマップには登録されているかもしれませんが、ホームページがないと、以下のような機会損失が生じている可能性がございます。
-・「どんな先生がいるのか」「どんな施術をしてくれるのか」を知りたい患者様が、情報不足で他院を選んでしまう
-・Googleで「地域名 + 整骨院」と検索しても、貴院の情報が上位に出てこない
-・口コミを書こうとしても、貴院の情報ページが見つからない
-弊社では、整骨院専門で5ページ程度のホームページ制作を98,000円（税込）〜で承っております。スマホ対応、問い合わせフォーム、電話・メール導線、Googleマップ連携、基本SEO設定、公開後1か月サポートが含まれております。
-ホームページだけでなく、Googleビジネスプロフィールの整備、LINE予約導線、Instagram初期設計、チラシ・名刺制作など、施術以外の集客業務を丸ごとサポートしております。
-ご興味がございましたら、貴院の状況に合わせた提案を無料でお作りいたします。お気軽にご連絡ください。
-━━━━━━━━━━━━━━━━━━━━━━
-WEBBRIO
-代表　柴藤
-TEL: 070-7615-5231
-https://seikotsuinweb.com/
-━━━━━━━━━━━━━━━━━━━━━━</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>ちくさ接骨院様｜Web集客に関するご提案</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="409.6" customHeight="1">
-      <c r="A13" t="n">
-        <v>24</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>しんもりやま整骨院</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>愛知県</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>名古屋市守山区</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>新守町6-1</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>電話</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>052-778-8880</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>【HP未確認】2026年1月開業。新守山駅徒歩1分</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>しんもりやま整骨院
-ご担当者様
-突然のご連絡失礼いたします。
-整骨院・接骨院専門のホームページ制作・集客支援を行っております、WEBBRIOの柴藤と申します。
-新守山エリアで2026年1月に開業されたとのこと、おめでとうございます。開業直後でお忙しい日々をお過ごしのことと存じます。
-突然ではございますが、貴院のホームページについてお伺いしたくご連絡いたしました。
-「新守山 整骨院」「名古屋市守山区 整体」などで検索したところ、貴院の公式ホームページが見当たらない状況でした。Googleマップには登録されているかもしれませんが、ホームページがないと、以下のような機会損失が生じている可能性がございます。
-・「どんな先生がいるのか」「どんな施術をしてくれるのか」を知りたい患者様が、情報不足で他院を選んでしまう
-・Googleで「地域名 + 整骨院」と検索しても、貴院の情報が上位に出てこない
-・口コミを書こうとしても、貴院の情報ページが見つからない
-弊社では、整骨院専門で5ページ程度のホームページ制作を98,000円（税込）〜で承っております。スマホ対応、問い合わせフォーム、電話・メール導線、Googleマップ連携、基本SEO設定、公開後1か月サポートが含まれております。
-ホームページだけでなく、Googleビジネスプロフィールの整備、LINE予約導線、Instagram初期設計、チラシ・名刺制作など、施術以外の集客業務を丸ごとサポートしております。
-ご興味がございましたら、貴院の状況に合わせた提案を無料でお作りいたします。お気軽にご連絡ください。
-━━━━━━━━━━━━━━━━━━━━━━
-WEBBRIO
-代表　柴藤
-TEL: 070-7615-5231
-https://seikotsuinweb.com/
-━━━━━━━━━━━━━━━━━━━━━━</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>しんもりやま整骨院様｜Web集客に関するご提案</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="409.6" customHeight="1">
-      <c r="A14" t="n">
-        <v>25</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>鍼灸整骨院三六 福岡南院</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>福岡県</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>福岡市南区</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>老司2-4-27</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>3</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>LINE・電話</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>https://tir-sanroku.jp/shop/fukuoka/</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>https://tir-sanroku.jp/shop/fukuoka/</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>三六グループ福岡新院。LINE予約可</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>鍼灸整骨院三六 福岡南院
-ご担当者様
-突然のご連絡失礼いたします。
-整骨院・接骨院専門のホームページ制作・集客支援を行っております、WEBBRIOの柴藤と申します。
-貴院のホームページを拝見いたしました。鍼灸整骨院三六グループとして全国展開されている実績は素晴らしく、LINE予約にも対応されており、患者様の利便性をしっかり考えていらっしゃいます。
-2026年4月に福岡南区に新院をオープンされたとのこと、おめでとうございます。
-失礼ながら、Web集客の観点から気になった点がございました。
-福岡南院は新しい院のため、「福岡市南区 整骨院」「老司 鍼灸」などの地域キーワードでの検索順位がまだ確立されていない状態です。グループサイトとは別に、福岡南院専用のランディングページを充実させることで、地域SEOの効果を高められます。
-また、開業初期から口コミを増やす仕組みを作っておくと、早い段階で地域での認知度を上げられます。
-弊社では、HP制作・改善だけでなく、Googleマップ対策、LINE予約導線、Instagram運用など、施術以外の集客業務を丸ごとサポートしております。
-ご興味がございましたら、貴院専用の改善プランを無料でお作りいたします。お気軽にご連絡ください。
-━━━━━━━━━━━━━━━━━━━━━━
-WEBBRIO
-代表　柴藤
-TEL: 070-7615-5231
-https://seikotsuinweb.com/
-━━━━━━━━━━━━━━━━━━━━━━</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>鍼灸整骨院三六 福岡南院様｜Web集客に関するご提案</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="409.6" customHeight="1">
-      <c r="A15" t="n">
-        <v>26</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>なぎさ接骨院・鍼灸院</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>広島県</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>広島市東区</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>牛田本町2-8-5</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>3</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>LINE・電話</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>https://nagisasekkotsuin.jp/</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>https://nagisasekkotsuin.jp/</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>2026年4月開業。公式HP有、LINE予約対応</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>なぎさ接骨院・鍼灸院
-ご担当者様
-突然のご連絡失礼いたします。
-整骨院・接骨院専門のホームページ制作・集客支援を行っております、WEBBRIOの柴藤と申します。
-貴院のホームページを拝見いたしました。2026年4月に広島市東区牛田本町で開業されたとのこと、おめでとうございます。LINE予約にも対応されており、患者様の利便性をしっかり考えていらっしゃいます。
-失礼ながら、Web集客の観点から気になった点がございました。
-開業間もないため、「牛田 整骨院」「広島市東区 鍼灸」などの地域キーワードでの検索順位がまだ確立されていない状態です。ホームページのSEO対策を強化したり、Googleビジネスプロフィールの投稿を継続的に行うことで、地域検索での露出を高められます。
-また、開業初期から口コミを増やす仕組みを作っておくと、早い段階で地域での認知度を上げられます。
-弊社では、HP改善だけでなく、Googleマップ対策、LINE予約導線、Instagram運用、チラシ制作など、施術以外の集客業務を丸ごとサポートしております。
-ご興味がございましたら、貴院専用の改善プランを無料でお作りいたします。お気軽にご連絡ください。
-━━━━━━━━━━━━━━━━━━━━━━
-WEBBRIO
-代表　柴藤
-TEL: 070-7615-5231
-https://seikotsuinweb.com/
-━━━━━━━━━━━━━━━━━━━━━━</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>なぎさ接骨院・鍼灸院様｜Web集客に関するご提案</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="409.6" customHeight="1">
-      <c r="A16" t="n">
-        <v>27</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>ひろがる接骨院 広島スタジアム前院</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>広島県</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>広島市南区</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>南蟹屋1-1-25</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>5</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>LINE・電話・HotPepper</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>https://hirogaru-hiroshima.com/</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>https://hirogaru-hiroshima.com/</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>充実した公式HP。新規制作対象外だがコンサル提案可</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>ひろがる接骨院 広島スタジアム前院
-ご担当者様
-突然のご連絡失礼いたします。
-整骨院・接骨院専門のホームページ制作・集客支援を行っております、WEBBRIOの柴藤と申します。
-貴院のホームページを拝見いたしました。非常にクオリティの高い公式サイトをお持ちで、LINE予約やHotPepper連携など集客導線も充実されていらっしゃいます。
-正直なところ、HP制作のご提案というよりは、現在の高品質なサイトをさらに活かすご提案をさせていただければと存じます。
-例えば：
-・Googleビジネスプロフィールの投稿代行や口コミ促進施策
-・Instagram運用代行
-・チラシ・リーフレット制作
-・Google広告やInstagram広告の運用
-など、施術以外の集客業務をお任せいただくことで、先生方が施術に集中できる環境を整えるお手伝いが可能です。
-ご興味がございましたら、お気軽にご連絡ください。
-━━━━━━━━━━━━━━━━━━━━━━
-WEBBRIO
-代表　柴藤
-TEL: 070-7615-5231
-https://seikotsuinweb.com/
-━━━━━━━━━━━━━━━━━━━━━━</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>ひろがる接骨院 広島スタジアム前院様｜Web集客に関するご提案</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="409.6" customHeight="1">
-      <c r="A17" t="n">
-        <v>28</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>with.鍼灸整骨院 西明石院</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>兵庫県</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>明石市</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>和坂13-6 プラスパ西明石102</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>3</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>LINE・電話</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>https://with-seikotsuin.com/</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>https://with-seikotsuin.com/</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>2026年6月開業。グループ公式HP有</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>with.鍼灸整骨院 西明石院
-ご担当者様
-突然のご連絡失礼いたします。
-整骨院・接骨院専門のホームページ制作・集客支援を行っております、WEBBRIOの柴藤と申します。
-貴院のホームページを拝見いたしました。2026年6月に西明石で開業されたとのこと、おめでとうございます。グループとして統一されたブランディングと、LINE予約対応など患者様目線のサービスが素晴らしいです。
-失礼ながら、Web集客の観点から気になった点がございました。
-開業間もないため、「西明石 整骨院」「明石市 鍼灸」などの地域キーワードでの検索順位がまだ確立されていない状態です。グループサイトに加えて、西明石院専用のランディングページを充実させることで、地域SEOの効果を高められます。
-また、開業初期から口コミを増やす仕組みを作っておくと、早い段階で地域での認知度を上げられます。
-弊社では、HP制作・改善だけでなく、Googleマップ対策、LINE予約導線、Instagram運用、チラシ制作など、施術以外の集客業務を丸ごとサポートしております。
-ご興味がございましたら、貴院専用の改善プランを無料でお作りいたします。お気軽にご連絡ください。
-━━━━━━━━━━━━━━━━━━━━━━
-WEBBRIO
-代表　柴藤
-TEL: 070-7615-5231
-https://seikotsuinweb.com/
-━━━━━━━━━━━━━━━━━━━━━━</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>with.鍼灸整骨院 西明石院様｜Web集客に関するご提案</t>
-        </is>
-      </c>
-    </row>
+    <row r="2" ht="200" customHeight="1"/>
+    <row r="3" ht="200" customHeight="1"/>
+    <row r="4" ht="200" customHeight="1"/>
+    <row r="5" ht="409.6" customHeight="1"/>
+    <row r="6" ht="409.6" customHeight="1"/>
+    <row r="7" ht="409.6" customHeight="1"/>
+    <row r="8" ht="409.6" customHeight="1"/>
+    <row r="9" ht="409.6" customHeight="1"/>
+    <row r="10" ht="409.6" customHeight="1"/>
+    <row r="11" ht="409.6" customHeight="1"/>
+    <row r="12" ht="409.6" customHeight="1"/>
+    <row r="13" ht="409.6" customHeight="1"/>
+    <row r="14" ht="409.6" customHeight="1"/>
+    <row r="15" ht="409.6" customHeight="1"/>
+    <row r="16" ht="409.6" customHeight="1"/>
+    <row r="17" ht="409.6" customHeight="1"/>
     <row r="18" ht="409.6" customHeight="1"/>
     <row r="19" ht="409.6" customHeight="1"/>
     <row r="20" ht="409.6" customHeight="1"/>
@@ -1902,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N45"/>
+  <dimension ref="A1:N61"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5579,6 +4247,1354 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>24</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>しんもりやま整骨院</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>名古屋市守山区</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>新守町6-1</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>電話のみ（サイトなし）</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>052-778-8880</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>【HP未確認】2026年1月開業。新守山駅徒歩1分</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>しんもりやま整骨院
+ご担当者様
+突然のご連絡失礼いたします。
+整骨院・接骨院専門のホームページ制作・集客支援を行っております、WEBBRIOの柴藤と申します。
+新守山エリアで2026年1月に開業されたとのこと、おめでとうございます。開業直後でお忙しい日々をお過ごしのことと存じます。
+突然ではございますが、貴院のホームページについてお伺いしたくご連絡いたしました。
+「新守山 整骨院」「名古屋市守山区 整体」などで検索したところ、貴院の公式ホームページが見当たらない状況でした。Googleマップには登録されているかもしれませんが、ホームページがないと、以下のような機会損失が生じている可能性がございます。
+・「どんな先生がいるのか」「どんな施術をしてくれるのか」を知りたい患者様が、情報不足で他院を選んでしまう
+・Googleで「地域名 + 整骨院」と検索しても、貴院の情報が上位に出てこない
+・口コミを書こうとしても、貴院の情報ページが見つからない
+弊社では、整骨院専門で5ページ程度のホームページ制作を98,000円（税込）〜で承っております。スマホ対応、問い合わせフォーム、電話・メール導線、Googleマップ連携、基本SEO設定、公開後1か月サポートが含まれております。
+ホームページだけでなく、Googleビジネスプロフィールの整備、LINE予約導線、Instagram初期設計、チラシ・名刺制作など、施術以外の集客業務を丸ごとサポートしております。
+ご興味がございましたら、貴院の状況に合わせた提案を無料でお作りいたします。お気軽にご連絡ください。
+━━━━━━━━━━━━━━━━━━━━━━
+WEBBRIO
+代表　柴藤
+TEL: 070-7615-5231
+https://seikotsuinweb.com/
+━━━━━━━━━━━━━━━━━━━━━━</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>しんもりやま整骨院様｜Web集客に関するご提案</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>23</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ちくさ接骨院</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>名古屋市千種区</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>千種1-16-16</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>電話のみ（サイトなし）</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>【HP未確認】2026年3月開業。千種エリア</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>ちくさ接骨院
+ご担当者様
+突然のご連絡失礼いたします。
+整骨院・接骨院専門のホームページ制作・集客支援を行っております、WEBBRIOの柴藤と申します。
+千種エリアで2026年3月に開業されたとのこと、おめでとうございます。開業直後でお忙しい日々をお過ごしのことと存じます。
+突然ではございますが、貴院のホームページについてお伺いしたくご連絡いたしました。
+「千種 整骨院」「名古屋市千種区 整体」などで検索したところ、貴院の公式ホームページが見当たらない状況でした。Googleマップには登録されているかもしれませんが、ホームページがないと、以下のような機会損失が生じている可能性がございます。
+・「どんな先生がいるのか」「どんな施術をしてくれるのか」を知りたい患者様が、情報不足で他院を選んでしまう
+・Googleで「地域名 + 整骨院」と検索しても、貴院の情報が上位に出てこない
+・口コミを書こうとしても、貴院の情報ページが見つからない
+弊社では、整骨院専門で5ページ程度のホームページ制作を98,000円（税込）〜で承っております。スマホ対応、問い合わせフォーム、電話・メール導線、Googleマップ連携、基本SEO設定、公開後1か月サポートが含まれております。
+ホームページだけでなく、Googleビジネスプロフィールの整備、LINE予約導線、Instagram初期設計、チラシ・名刺制作など、施術以外の集客業務を丸ごとサポートしております。
+ご興味がございましたら、貴院の状況に合わせた提案を無料でお作りいたします。お気軽にご連絡ください。
+━━━━━━━━━━━━━━━━━━━━━━
+WEBBRIO
+代表　柴藤
+TEL: 070-7615-5231
+https://seikotsuinweb.com/
+━━━━━━━━━━━━━━━━━━━━━━</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>ちくさ接骨院様｜Web集客に関するご提案</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>22</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>いまいけ接骨院</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>名古屋市千種区</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>今池3-2-9 ママビル1F</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>電話のみ（サイトなし）</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>052-732-8727</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>【HP未確認】2026年3月開業。今池エリア。Facebookあり</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>いまいけ接骨院
+ご担当者様
+突然のご連絡失礼いたします。
+整骨院・接骨院専門のホームページ制作・集客支援を行っております、WEBBRIOの柴藤と申します。
+今池エリアで2026年3月に開業されたとのこと、おめでとうございます。開業直後でお忙しい日々をお過ごしのことと存じます。
+突然ではございますが、貴院のホームページについてお伺いしたくご連絡いたしました。
+「今池 整骨院」「名古屋市千種区 整体」などで検索したところ、貴院の公式ホームページが見当たらない状況でした。Googleマップには登録されているかもしれませんが、ホームページがないと、以下のような機会損失が生じている可能性がございます。
+・「どんな先生がいるのか」「どんな施術をしてくれるのか」を知りたい患者様が、情報不足で他院を選んでしまう
+・Googleで「地域名 + 整骨院」と検索しても、貴院の情報が上位に出てこない
+・口コミを書こうとしても、貴院の情報ページが見つからない
+弊社では、整骨院専門で5ページ程度のホームページ制作を98,000円（税込）〜で承っております。スマホ対応、問い合わせフォーム、電話・メール導線、Googleマップ連携、基本SEO設定、公開後1か月サポートが含まれております。
+ホームページだけでなく、Googleビジネスプロフィールの整備、LINE予約導線、Instagram初期設計、チラシ・名刺制作など、施術以外の集客業務を丸ごとサポートしております。
+ご興味がございましたら、貴院の状況に合わせた提案を無料でお作りいたします。お気軽にご連絡ください。
+━━━━━━━━━━━━━━━━━━━━━━
+WEBBRIO
+代表　柴藤
+TEL: 070-7615-5231
+https://seikotsuinweb.com/
+━━━━━━━━━━━━━━━━━━━━━━</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>いまいけ接骨院様｜Web集客に関するご提案</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>21</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>まつおか整骨院・鍼灸院</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>福岡県</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>福岡市西区</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>今宿1-5-30 第1井原ビル102</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>電話のみ（サイトなし）</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>【HP未確認】2026年4月開業。今宿エリア</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>まつおか整骨院・鍼灸院
+ご担当者様
+突然のご連絡失礼いたします。
+整骨院・接骨院専門のホームページ制作・集客支援を行っております、WEBBRIOの柴藤と申します。
+今宿エリアで2026年4月に開業されたとのこと、おめでとうございます。開業直後でお忙しい日々をお過ごしのことと存じます。
+突然ではございますが、貴院のホームページについてお伺いしたくご連絡いたしました。
+「今宿 整骨院」「福岡市西区 整体」などで検索したところ、貴院の公式ホームページが見当たらない状況でした。Googleマップには登録されているかもしれませんが、ホームページがないと、以下のような機会損失が生じている可能性がございます。
+・「どんな先生がいるのか」「どんな施術をしてくれるのか」を知りたい患者様が、情報不足で他院を選んでしまう
+・Googleで「地域名 + 整骨院」と検索しても、貴院の情報が上位に出てこない
+・口コミを書こうとしても、貴院の情報ページが見つからない
+弊社では、整骨院専門で5ページ程度のホームページ制作を98,000円（税込）〜で承っております。スマホ対応、問い合わせフォーム、電話・メール導線、Googleマップ連携、基本SEO設定、公開後1か月サポートが含まれております。
+ホームページだけでなく、Googleビジネスプロフィールの整備、LINE予約導線、Instagram初期設計、チラシ・名刺制作など、施術以外の集客業務を丸ごとサポートしております。
+ご興味がございましたら、貴院の状況に合わせた提案を無料でお作りいたします。お気軽にご連絡ください。
+━━━━━━━━━━━━━━━━━━━━━━
+WEBBRIO
+代表　柴藤
+TEL: 070-7615-5231
+https://seikotsuinweb.com/
+━━━━━━━━━━━━━━━━━━━━━━</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>まつおか整骨院・鍼灸院様｜Web集客に関するご提案</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>20</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>野方たかまる整骨院</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>福岡県</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>福岡市西区</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>野方1-17-29 野方宮本ビル1階2号</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>電話のみ（サイトなし）</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>【HP未確認】2026年4月開業。野方エリア</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>野方たかまる整骨院
+ご担当者様
+突然のご連絡失礼いたします。
+整骨院・接骨院専門のホームページ制作・集客支援を行っております、WEBBRIOの柴藤と申します。
+野方エリアで2026年4月に開業されたとのこと、おめでとうございます。開業直後でお忙しい日々をお過ごしのことと存じます。
+突然ではございますが、貴院のホームページについてお伺いしたくご連絡いたしました。
+「野方 整骨院」「福岡市西区 整体」などで検索したところ、貴院の公式ホームページが見当たらない状況でした。Googleマップには登録されているかもしれませんが、ホームページがないと、以下のような機会損失が生じている可能性がございます。
+・「どんな先生がいるのか」「どんな施術をしてくれるのか」を知りたい患者様が、情報不足で他院を選んでしまう
+・Googleで「地域名 + 整骨院」と検索しても、貴院の情報が上位に出てこない
+・口コミを書こうとしても、貴院の情報ページが見つからない
+弊社では、整骨院専門で5ページ程度のホームページ制作を98,000円（税込）〜で承っております。スマホ対応、問い合わせフォーム、電話・メール導線、Googleマップ連携、基本SEO設定、公開後1か月サポートが含まれております。
+ホームページだけでなく、Googleビジネスプロフィールの整備、LINE予約導線、Instagram初期設計、チラシ・名刺制作など、施術以外の集客業務を丸ごとサポートしております。
+ご興味がございましたら、貴院の状況に合わせた提案を無料でお作りいたします。お気軽にご連絡ください。
+━━━━━━━━━━━━━━━━━━━━━━
+WEBBRIO
+代表　柴藤
+TEL: 070-7615-5231
+https://seikotsuinweb.com/
+━━━━━━━━━━━━━━━━━━━━━━</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>野方たかまる整骨院様｜Web集客に関するご提案</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>19</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>賀茂整骨院</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>福岡県</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>福岡市早良区</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>田隈1-25-20</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>電話のみ（サイトなし）</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>【HP未確認】2026年3月開業。田隈エリア</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>賀茂整骨院
+ご担当者様
+突然のご連絡失礼いたします。
+整骨院・接骨院専門のホームページ制作・集客支援を行っております、WEBBRIOの柴藤と申します。
+田隈エリアで2026年3月に開業されたとのこと、おめでとうございます。開業直後でお忙しい日々をお過ごしのことと存じます。
+突然ではございますが、貴院のホームページについてお伺いしたくご連絡いたしました。
+「田隈 整骨院」「福岡市早良区 整体」などで検索したところ、貴院の公式ホームページが見当たらない状況でした。Googleマップには登録されているかもしれませんが、ホームページがないと、以下のような機会損失が生じている可能性がございます。
+・「どんな先生がいるのか」「どんな施術をしてくれるのか」を知りたい患者様が、情報不足で他院を選んでしまう
+・Googleで「地域名 + 整骨院」と検索しても、貴院の情報が上位に出てこない
+・口コミを書こうとしても、貴院の情報ページが見つからない
+弊社では、整骨院専門で5ページ程度のホームページ制作を98,000円（税込）〜で承っております。スマホ対応、問い合わせフォーム、電話・メール導線、Googleマップ連携、基本SEO設定、公開後1か月サポートが含まれております。
+ホームページだけでなく、Googleビジネスプロフィールの整備、LINE予約導線、Instagram初期設計、チラシ・名刺制作など、施術以外の集客業務を丸ごとサポートしております。
+ご興味がございましたら、貴院の状況に合わせた提案を無料でお作りいたします。お気軽にご連絡ください。
+━━━━━━━━━━━━━━━━━━━━━━
+WEBBRIO
+代表　柴藤
+TEL: 070-7615-5231
+https://seikotsuinweb.com/
+━━━━━━━━━━━━━━━━━━━━━━</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>賀茂整骨院様｜Web集客に関するご提案</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>18</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ますみ整骨院</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>福岡県</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>福岡市早良区</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>田村7-14-88</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>電話のみ（サイトなし）</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>092-982-4972</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>【HP未確認】2026年4月開業。田村エリア</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>ますみ整骨院
+ご担当者様
+突然のご連絡失礼いたします。
+整骨院・接骨院専門のホームページ制作・集客支援を行っております、WEBBRIOの柴藤と申します。
+田村エリアで2026年4月に開業されたとのこと、おめでとうございます。開業直後でお忙しい日々をお過ごしのことと存じます。
+突然ではございますが、貴院のホームページについてお伺いしたくご連絡いたしました。
+「田村 整骨院」「福岡市早良区 整体」などで検索したところ、貴院の公式ホームページが見当たらない状況でした。Googleマップには登録されているかもしれませんが、ホームページがないと、以下のような機会損失が生じている可能性がございます。
+・「どんな先生がいるのか」「どんな施術をしてくれるのか」を知りたい患者様が、情報不足で他院を選んでしまう
+・Googleで「地域名 + 整骨院」と検索しても、貴院の情報が上位に出てこない
+・口コミを書こうとしても、貴院の情報ページが見つからない
+弊社では、整骨院専門で5ページ程度のホームページ制作を98,000円（税込）〜で承っております。スマホ対応、問い合わせフォーム、電話・メール導線、Googleマップ連携、基本SEO設定、公開後1か月サポートが含まれております。
+ホームページだけでなく、Googleビジネスプロフィールの整備、LINE予約導線、Instagram初期設計、チラシ・名刺制作など、施術以外の集客業務を丸ごとサポートしております。
+ご興味がございましたら、貴院の状況に合わせた提案を無料でお作りいたします。お気軽にご連絡ください。
+━━━━━━━━━━━━━━━━━━━━━━
+WEBBRIO
+代表　柴藤
+TEL: 070-7615-5231
+https://seikotsuinweb.com/
+━━━━━━━━━━━━━━━━━━━━━━</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>ますみ整骨院様｜Web集客に関するご提案</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>17</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>三好整骨院</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>福岡県</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>福岡市城南区</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>七隈1-17-29</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>1</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>電話のみ（サイトなし）</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>092-843-0033</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>【HP未確認】2026年1月開業。七隈エリア</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>三好整骨院
+ご担当者様
+突然のご連絡失礼いたします。
+整骨院・接骨院専門のホームページ制作・集客支援を行っております、WEBBRIOの柴藤と申します。
+七隈エリアで2026年1月に開業されたとのこと、おめでとうございます。開業直後でお忙しい日々をお過ごしのことと存じます。
+突然ではございますが、貴院のホームページについてお伺いしたくご連絡いたしました。
+「七隈 整骨院」「福岡市城南区 整体」などで検索したところ、貴院の公式ホームページが見当たらない状況でした。Googleマップには登録されているかもしれませんが、ホームページがないと、以下のような機会損失が生じている可能性がございます。
+・「どんな先生がいるのか」「どんな施術をしてくれるのか」を知りたい患者様が、情報不足で他院を選んでしまう
+・Googleで「地域名 + 整骨院」と検索しても、貴院の情報が上位に出てこない
+・口コミを書こうとしても、貴院の情報ページが見つからない
+弊社では、整骨院専門で5ページ程度のホームページ制作を98,000円（税込）〜で承っております。スマホ対応、問い合わせフォーム、電話・メール導線、Googleマップ連携、基本SEO設定、公開後1か月サポートが含まれております。
+ホームページだけでなく、Googleビジネスプロフィールの整備、LINE予約導線、Instagram初期設計、チラシ・名刺制作など、施術以外の集客業務を丸ごとサポートしております。
+ご興味がございましたら、貴院の状況に合わせた提案を無料でお作りいたします。お気軽にご連絡ください。
+━━━━━━━━━━━━━━━━━━━━━━
+WEBBRIO
+代表　柴藤
+TEL: 070-7615-5231
+https://seikotsuinweb.com/
+━━━━━━━━━━━━━━━━━━━━━━</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>三好整骨院様｜Web集客に関するご提案</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>16</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>もとむう接骨院</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>福岡県</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>福岡市城南区</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>堤1-13-36 プラモール88 104号</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>1</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>電話のみ（サイトなし）</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>092-707-4353</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>【HP未確認】2026年1月開業。堤エリア</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>もとむう接骨院
+ご担当者様
+突然のご連絡失礼いたします。
+整骨院・接骨院専門のホームページ制作・集客支援を行っております、WEBBRIOの柴藤と申します。
+堤エリアで2026年1月に開業されたとのこと、おめでとうございます。開業直後でお忙しい日々をお過ごしのことと存じます。
+突然ではございますが、貴院のホームページについてお伺いしたくご連絡いたしました。
+「堤 整骨院」「福岡市城南区 整体」などで検索したところ、貴院の公式ホームページが見当たらない状況でした。Googleマップには登録されているかもしれませんが、ホームページがないと、以下のような機会損失が生じている可能性がございます。
+・「どんな先生がいるのか」「どんな施術をしてくれるのか」を知りたい患者様が、情報不足で他院を選んでしまう
+・Googleで「地域名 + 整骨院」と検索しても、貴院の情報が上位に出てこない
+・口コミを書こうとしても、貴院の情報ページが見つからない
+弊社では、整骨院専門で5ページ程度のホームページ制作を98,000円（税込）〜で承っております。スマホ対応、問い合わせフォーム、電話・メール導線、Googleマップ連携、基本SEO設定、公開後1か月サポートが含まれております。
+ホームページだけでなく、Googleビジネスプロフィールの整備、LINE予約導線、Instagram初期設計、チラシ・名刺制作など、施術以外の集客業務を丸ごとサポートしております。
+ご興味がございましたら、貴院の状況に合わせた提案を無料でお作りいたします。お気軽にご連絡ください。
+━━━━━━━━━━━━━━━━━━━━━━
+WEBBRIO
+代表　柴藤
+TEL: 070-7615-5231
+https://seikotsuinweb.com/
+━━━━━━━━━━━━━━━━━━━━━━</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>もとむう接骨院様｜Web集客に関するご提案</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>15</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>しまむら整骨院</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>福岡県</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>福岡市南区</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>大楠3-23-1-101</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>1</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>電話のみ（サイトなし）</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>092-874-3337</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>【HP未確認】2026年1月開業。大楠エリア</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>しまむら整骨院
+ご担当者様
+突然のご連絡失礼いたします。
+整骨院・接骨院専門のホームページ制作・集客支援を行っております、WEBBRIOの柴藤と申します。
+大楠エリアで2026年1月に開業されたとのこと、おめでとうございます。開業直後でお忙しい日々をお過ごしのことと存じます。
+突然ではございますが、貴院のホームページについてお伺いしたくご連絡いたしました。
+「大楠 整骨院」「福岡市南区 整体」などで検索したところ、貴院の公式ホームページが見当たらない状況でした。Googleマップには登録されているかもしれませんが、ホームページがないと、以下のような機会損失が生じている可能性がございます。
+・「どんな先生がいるのか」「どんな施術をしてくれるのか」を知りたい患者様が、情報不足で他院を選んでしまう
+・Googleで「地域名 + 整骨院」と検索しても、貴院の情報が上位に出てこない
+・口コミを書こうとしても、貴院の情報ページが見つからない
+弊社では、整骨院専門で5ページ程度のホームページ制作を98,000円（税込）〜で承っております。スマホ対応、問い合わせフォーム、電話・メール導線、Googleマップ連携、基本SEO設定、公開後1か月サポートが含まれております。
+ホームページだけでなく、Googleビジネスプロフィールの整備、LINE予約導線、Instagram初期設計、チラシ・名刺制作など、施術以外の集客業務を丸ごとサポートしております。
+ご興味がございましたら、貴院の状況に合わせた提案を無料でお作りいたします。お気軽にご連絡ください。
+━━━━━━━━━━━━━━━━━━━━━━
+WEBBRIO
+代表　柴藤
+TEL: 070-7615-5231
+https://seikotsuinweb.com/
+━━━━━━━━━━━━━━━━━━━━━━</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>しまむら整骨院様｜Web集客に関するご提案</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>14</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>柏原とみた整骨院</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>福岡県</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>福岡市南区</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>柏原6-19-8</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>1</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>電話のみ（サイトなし）</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>092-555-8641</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>【HP未確認】2026年3月開業。柏原エリア</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>柏原とみた整骨院
+ご担当者様
+突然のご連絡失礼いたします。
+整骨院・接骨院専門のホームページ制作・集客支援を行っております、WEBBRIOの柴藤と申します。
+柏原エリアで2026年3月に開業されたとのこと、おめでとうございます。開業直後でお忙しい日々をお過ごしのことと存じます。
+突然ではございますが、貴院のホームページについてお伺いしたくご連絡いたしました。
+「柏原 整骨院」「福岡市南区 整体」などで検索したところ、貴院の公式ホームページが見当たらない状況でした。Googleマップには登録されているかもしれませんが、ホームページがないと、以下のような機会損失が生じている可能性がございます。
+・「どんな先生がいるのか」「どんな施術をしてくれるのか」を知りたい患者様が、情報不足で他院を選んでしまう
+・Googleで「地域名 + 整骨院」と検索しても、貴院の情報が上位に出てこない
+・口コミを書こうとしても、貴院の情報ページが見つからない
+弊社では、整骨院専門で5ページ程度のホームページ制作を98,000円（税込）〜で承っております。スマホ対応、問い合わせフォーム、電話・メール導線、Googleマップ連携、基本SEO設定、公開後1か月サポートが含まれております。
+ホームページだけでなく、Googleビジネスプロフィールの整備、LINE予約導線、Instagram初期設計、チラシ・名刺制作など、施術以外の集客業務を丸ごとサポートしております。
+ご興味がございましたら、貴院の状況に合わせた提案を無料でお作りいたします。お気軽にご連絡ください。
+━━━━━━━━━━━━━━━━━━━━━━
+WEBBRIO
+代表　柴藤
+TEL: 070-7615-5231
+https://seikotsuinweb.com/
+━━━━━━━━━━━━━━━━━━━━━━</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>柏原とみた整骨院様｜Web集客に関するご提案</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>13</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>大名ふわり鍼灸院・整骨院</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>福岡県</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>福岡市中央区</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>大名1-9-45-308</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>電話のみ（サイトなし）</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>090-2357-1988</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>【HP未確認】2026年2月開業。大名エリア</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>大名ふわり鍼灸院・整骨院
+ご担当者様
+突然のご連絡失礼いたします。
+整骨院・接骨院専門のホームページ制作・集客支援を行っております、WEBBRIOの柴藤と申します。
+大名エリアで2026年2月に開業されたとのこと、おめでとうございます。開業直後でお忙しい日々をお過ごしのことと存じます。
+突然ではございますが、貴院のホームページについてお伺いしたくご連絡いたしました。
+「大名 整骨院」「福岡市中央区 整体」などで検索したところ、貴院の公式ホームページが見当たらない状況でした。Googleマップには登録されているかもしれませんが、ホームページがないと、以下のような機会損失が生じている可能性がございます。
+・「どんな先生がいるのか」「どんな施術をしてくれるのか」を知りたい患者様が、情報不足で他院を選んでしまう
+・Googleで「地域名 + 整骨院」と検索しても、貴院の情報が上位に出てこない
+・口コミを書こうとしても、貴院の情報ページが見つからない
+弊社では、整骨院専門で5ページ程度のホームページ制作を98,000円（税込）〜で承っております。スマホ対応、問い合わせフォーム、電話・メール導線、Googleマップ連携、基本SEO設定、公開後1か月サポートが含まれております。
+ホームページだけでなく、Googleビジネスプロフィールの整備、LINE予約導線、Instagram初期設計、チラシ・名刺制作など、施術以外の集客業務を丸ごとサポートしております。
+ご興味がございましたら、貴院の状況に合わせた提案を無料でお作りいたします。お気軽にご連絡ください。
+━━━━━━━━━━━━━━━━━━━━━━
+WEBBRIO
+代表　柴藤
+TEL: 070-7615-5231
+https://seikotsuinweb.com/
+━━━━━━━━━━━━━━━━━━━━━━</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>大名ふわり鍼灸院・整骨院様｜Web集客に関するご提案</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>25</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>鍼灸整骨院三六 福岡南院</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>福岡県</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>福岡市南区</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>老司2-4-27</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>3</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>手動送信（フォームなし）</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>https://tir-sanroku.jp/shop/fukuoka/</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>https://tir-sanroku.jp/shop/fukuoka/</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>三六グループ福岡新院。LINE予約可</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>鍼灸整骨院三六 福岡南院
+ご担当者様
+突然のご連絡失礼いたします。
+整骨院・接骨院専門のホームページ制作・集客支援を行っております、WEBBRIOの柴藤と申します。
+貴院のホームページを拝見いたしました。鍼灸整骨院三六グループとして全国展開されている実績は素晴らしく、LINE予約にも対応されており、患者様の利便性をしっかり考えていらっしゃいます。
+2026年4月に福岡南区に新院をオープンされたとのこと、おめでとうございます。
+失礼ながら、Web集客の観点から気になった点がございました。
+福岡南院は新しい院のため、「福岡市南区 整骨院」「老司 鍼灸」などの地域キーワードでの検索順位がまだ確立されていない状態です。グループサイトとは別に、福岡南院専用のランディングページを充実させることで、地域SEOの効果を高められます。
+また、開業初期から口コミを増やす仕組みを作っておくと、早い段階で地域での認知度を上げられます。
+弊社では、HP制作・改善だけでなく、Googleマップ対策、LINE予約導線、Instagram運用など、施術以外の集客業務を丸ごとサポートしております。
+ご興味がございましたら、貴院専用の改善プランを無料でお作りいたします。お気軽にご連絡ください。
+━━━━━━━━━━━━━━━━━━━━━━
+WEBBRIO
+代表　柴藤
+TEL: 070-7615-5231
+https://seikotsuinweb.com/
+━━━━━━━━━━━━━━━━━━━━━━</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>鍼灸整骨院三六 福岡南院様｜Web集客に関するご提案</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>26</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>なぎさ接骨院・鍼灸院</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>広島県</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>広島市東区</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>牛田本町2-8-5</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>3</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>手動送信（フォームなし）</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>https://nagisasekkotsuin.jp/</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>https://nagisasekkotsuin.jp/</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>2026年4月開業。公式HP有、LINE予約対応</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>なぎさ接骨院・鍼灸院
+ご担当者様
+突然のご連絡失礼いたします。
+整骨院・接骨院専門のホームページ制作・集客支援を行っております、WEBBRIOの柴藤と申します。
+貴院のホームページを拝見いたしました。2026年4月に広島市東区牛田本町で開業されたとのこと、おめでとうございます。LINE予約にも対応されており、患者様の利便性をしっかり考えていらっしゃいます。
+失礼ながら、Web集客の観点から気になった点がございました。
+開業間もないため、「牛田 整骨院」「広島市東区 鍼灸」などの地域キーワードでの検索順位がまだ確立されていない状態です。ホームページのSEO対策を強化したり、Googleビジネスプロフィールの投稿を継続的に行うことで、地域検索での露出を高められます。
+また、開業初期から口コミを増やす仕組みを作っておくと、早い段階で地域での認知度を上げられます。
+弊社では、HP改善だけでなく、Googleマップ対策、LINE予約導線、Instagram運用、チラシ制作など、施術以外の集客業務を丸ごとサポートしております。
+ご興味がございましたら、貴院専用の改善プランを無料でお作りいたします。お気軽にご連絡ください。
+━━━━━━━━━━━━━━━━━━━━━━
+WEBBRIO
+代表　柴藤
+TEL: 070-7615-5231
+https://seikotsuinweb.com/
+━━━━━━━━━━━━━━━━━━━━━━</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>なぎさ接骨院・鍼灸院様｜Web集客に関するご提案</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>27</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>ひろがる接骨院 広島スタジアム前院</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>広島県</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>広島市南区</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>南蟹屋1-1-25</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>5</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>手動送信（フォームなし）</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>https://hirogaru-hiroshima.com/</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>https://hirogaru-hiroshima.com/</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>充実した公式HP。新規制作対象外だがコンサル提案可</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>ひろがる接骨院 広島スタジアム前院
+ご担当者様
+突然のご連絡失礼いたします。
+整骨院・接骨院専門のホームページ制作・集客支援を行っております、WEBBRIOの柴藤と申します。
+貴院のホームページを拝見いたしました。非常にクオリティの高い公式サイトをお持ちで、LINE予約やHotPepper連携など集客導線も充実されていらっしゃいます。
+正直なところ、HP制作のご提案というよりは、現在の高品質なサイトをさらに活かすご提案をさせていただければと存じます。
+例えば：
+・Googleビジネスプロフィールの投稿代行や口コミ促進施策
+・Instagram運用代行
+・チラシ・リーフレット制作
+・Google広告やInstagram広告の運用
+など、施術以外の集客業務をお任せいただくことで、先生方が施術に集中できる環境を整えるお手伝いが可能です。
+ご興味がございましたら、お気軽にご連絡ください。
+━━━━━━━━━━━━━━━━━━━━━━
+WEBBRIO
+代表　柴藤
+TEL: 070-7615-5231
+https://seikotsuinweb.com/
+━━━━━━━━━━━━━━━━━━━━━━</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>ひろがる接骨院 広島スタジアム前院様｜Web集客に関するご提案</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>28</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>with.鍼灸整骨院 西明石院</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>兵庫県</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>明石市</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>和坂13-6 プラスパ西明石102</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>3</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>手動送信（メッセージ欄なし）</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>https://with-seikotsuin.com/</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>https://with-seikotsuin.com/</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>2026年6月開業。グループ公式HP有</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>with.鍼灸整骨院 西明石院
+ご担当者様
+突然のご連絡失礼いたします。
+整骨院・接骨院専門のホームページ制作・集客支援を行っております、WEBBRIOの柴藤と申します。
+貴院のホームページを拝見いたしました。2026年6月に西明石で開業されたとのこと、おめでとうございます。グループとして統一されたブランディングと、LINE予約対応など患者様目線のサービスが素晴らしいです。
+失礼ながら、Web集客の観点から気になった点がございました。
+開業間もないため、「西明石 整骨院」「明石市 鍼灸」などの地域キーワードでの検索順位がまだ確立されていない状態です。グループサイトに加えて、西明石院専用のランディングページを充実させることで、地域SEOの効果を高められます。
+また、開業初期から口コミを増やす仕組みを作っておくと、早い段階で地域での認知度を上げられます。
+弊社では、HP制作・改善だけでなく、Googleマップ対策、LINE予約導線、Instagram運用、チラシ制作など、施術以外の集客業務を丸ごとサポートしております。
+ご興味がございましたら、貴院専用の改善プランを無料でお作りいたします。お気軽にご連絡ください。
+━━━━━━━━━━━━━━━━━━━━━━
+WEBBRIO
+代表　柴藤
+TEL: 070-7615-5231
+https://seikotsuinweb.com/
+━━━━━━━━━━━━━━━━━━━━━━</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>with.鍼灸整骨院 西明石院様｜Web集客に関するご提案</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
